--- a/string-manipulation/test-output/test-results.xlsx
+++ b/string-manipulation/test-output/test-results.xlsx
@@ -13,10 +13,10 @@
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="StringLoopReverse" r:id="rId8" sheetId="30"/>
-    <sheet name="StringRecursionReverse" r:id="rId9" sheetId="31"/>
-    <sheet name="StringStreamReverse" r:id="rId10" sheetId="32"/>
-    <sheet name="StringBufferReverse" r:id="rId11" sheetId="33"/>
+    <sheet name="StringLoopReverse" r:id="rId8" sheetId="34"/>
+    <sheet name="StringRecursionReverse" r:id="rId9" sheetId="35"/>
+    <sheet name="StringStreamReverse" r:id="rId10" sheetId="36"/>
+    <sheet name="StringBufferReverse" r:id="rId11" sheetId="37"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="18">
   <si>
     <t>Name</t>
   </si>
@@ -97,7 +97,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -124,6 +124,26 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -186,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -200,6 +220,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,7 +556,7 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -546,22 +570,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="9">
+      <c r="A1" t="s" s="13">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="9">
+      <c r="B1" t="s" s="13">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="9">
+      <c r="C1" t="s" s="13">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="9">
+      <c r="D1" t="s" s="13">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="9">
+      <c r="E1" t="s" s="13">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="9">
+      <c r="F1" t="s" s="13">
         <v>5</v>
       </c>
     </row>
@@ -668,7 +692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -682,22 +706,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="10">
+      <c r="A1" t="s" s="14">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="10">
+      <c r="B1" t="s" s="14">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="10">
+      <c r="C1" t="s" s="14">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="10">
+      <c r="D1" t="s" s="14">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="10">
+      <c r="E1" t="s" s="14">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="10">
+      <c r="F1" t="s" s="14">
         <v>5</v>
       </c>
     </row>
@@ -804,7 +828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -818,22 +842,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="11">
+      <c r="A1" t="s" s="15">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="11">
+      <c r="B1" t="s" s="15">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="11">
+      <c r="C1" t="s" s="15">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="11">
+      <c r="D1" t="s" s="15">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="11">
+      <c r="E1" t="s" s="15">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="11">
+      <c r="F1" t="s" s="15">
         <v>5</v>
       </c>
     </row>
@@ -854,7 +878,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="3">
@@ -940,7 +964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -954,22 +978,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="12">
+      <c r="A1" t="s" s="16">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="12">
+      <c r="B1" t="s" s="16">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="12">
+      <c r="C1" t="s" s="16">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="12">
+      <c r="D1" t="s" s="16">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="12">
+      <c r="E1" t="s" s="16">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="12">
+      <c r="F1" t="s" s="16">
         <v>5</v>
       </c>
     </row>
